--- a/datasets_test.xlsx
+++ b/datasets_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6AC618-7309-44C7-B18E-E639BBCC32EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14910967-11FE-4473-83F3-D73F1E989E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19155" yWindow="2250" windowWidth="18885" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="434">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1427,6 +1427,29 @@
   </si>
   <si>
     <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_512\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>data type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>real-2d</t>
+  </si>
+  <si>
+    <t>real-2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simu-3d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>real-3d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(31,25,25)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2161,3229 +2184,3392 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S110"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.125" customWidth="1"/>
-    <col min="2" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="3" width="2.5" customWidth="1"/>
-    <col min="4" max="4" width="3.375" customWidth="1"/>
-    <col min="5" max="5" width="2.25" customWidth="1"/>
-    <col min="6" max="6" width="2.375" customWidth="1"/>
-    <col min="7" max="9" width="4.25" customWidth="1"/>
-    <col min="10" max="11" width="9.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="113.75" customWidth="1"/>
-    <col min="14" max="14" width="101" customWidth="1"/>
-    <col min="15" max="15" width="9.375" customWidth="1"/>
-    <col min="17" max="17" width="8" customWidth="1"/>
+    <col min="2" max="2" width="10.375" customWidth="1"/>
+    <col min="3" max="3" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="2.5" customWidth="1"/>
+    <col min="5" max="5" width="3.375" customWidth="1"/>
+    <col min="6" max="6" width="2.25" customWidth="1"/>
+    <col min="7" max="7" width="2.375" customWidth="1"/>
+    <col min="8" max="10" width="4.25" customWidth="1"/>
+    <col min="11" max="12" width="9.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="113.75" customWidth="1"/>
+    <col min="15" max="15" width="101" customWidth="1"/>
+    <col min="16" max="16" width="9.375" customWidth="1"/>
+    <col min="18" max="18" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1" t="s">
         <v>301</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>422</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>425</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
       <c r="B2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C2" t="s">
         <v>303</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
+      <c r="J2">
+        <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>376</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>154</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>155</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>156</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>34</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>62.6</v>
       </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C3" t="s">
         <v>303</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>37</v>
       </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>7</v>
+      <c r="J3">
+        <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>377</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>157</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>158</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>156</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>34</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>62.6</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4" t="s">
         <v>303</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>37</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>7</v>
+      <c r="J4">
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>378</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>159</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>160</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>156</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>34</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>62.6</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" t="s">
         <v>303</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>37</v>
       </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>7</v>
+      <c r="J5">
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>379</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>161</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>162</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>156</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>34</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>62.6</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C6" t="s">
         <v>303</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>7</v>
+      <c r="J6">
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>380</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>163</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>164</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>156</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>34</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>62.6</v>
       </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
       <c r="B7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C7" t="s">
         <v>303</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
         <v>37</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>7</v>
+      <c r="J7">
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>381</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>165</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>166</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>156</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>34</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>62.6</v>
       </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>45</v>
       </c>
       <c r="B8" t="s">
+        <v>430</v>
+      </c>
+      <c r="C8" t="s">
         <v>303</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
         <v>37</v>
       </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>7</v>
+      <c r="J8">
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>382</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>167</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>168</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>156</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>34</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>62.6</v>
       </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>46</v>
       </c>
       <c r="B9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C9" t="s">
         <v>303</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
         <v>37</v>
       </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>7</v>
+      <c r="J9">
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>383</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>169</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>170</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>156</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>34</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>62.6</v>
       </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
       <c r="B10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C10" t="s">
         <v>303</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
         <v>37</v>
       </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>7</v>
+      <c r="J10">
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>384</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>171</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>172</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>156</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>34</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>62.6</v>
       </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>27</v>
       </c>
       <c r="B11" t="s">
+        <v>430</v>
+      </c>
+      <c r="C11" t="s">
         <v>304</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>7</v>
+      <c r="J11">
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>385</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>173</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>174</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>175</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>34</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>62.6</v>
       </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>48</v>
       </c>
       <c r="B12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" t="s">
         <v>304</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>37</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>7</v>
+      <c r="J12">
+        <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>386</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>176</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>177</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>175</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>34</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>62.6</v>
       </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>49</v>
       </c>
       <c r="B13" t="s">
+        <v>430</v>
+      </c>
+      <c r="C13" t="s">
         <v>304</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
         <v>37</v>
       </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>7</v>
+      <c r="J13">
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>387</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>178</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>179</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>175</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>34</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>62.6</v>
       </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>50</v>
       </c>
       <c r="B14" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" t="s">
         <v>304</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
         <v>37</v>
       </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>7</v>
+      <c r="J14">
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>388</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>180</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>181</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>175</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>34</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>62.6</v>
       </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>51</v>
       </c>
       <c r="B15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C15" t="s">
         <v>304</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
         <v>37</v>
       </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>7</v>
+      <c r="J15">
+        <v>0</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>389</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>182</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>183</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>175</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>34</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>62.6</v>
       </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>52</v>
       </c>
       <c r="B16" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" t="s">
         <v>304</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
         <v>37</v>
       </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>7</v>
+      <c r="J16">
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>390</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>184</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>185</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>175</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>34</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>62.6</v>
       </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>53</v>
       </c>
       <c r="B17" t="s">
+        <v>430</v>
+      </c>
+      <c r="C17" t="s">
         <v>304</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
         <v>37</v>
       </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>7</v>
+      <c r="J17">
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>391</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>186</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>187</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>175</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>34</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>62.6</v>
       </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>54</v>
       </c>
       <c r="B18" t="s">
+        <v>430</v>
+      </c>
+      <c r="C18" t="s">
         <v>304</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
         <v>37</v>
       </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>7</v>
+      <c r="J18">
+        <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>392</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>188</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>189</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>175</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>34</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>62.6</v>
       </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
       <c r="B19" t="s">
+        <v>430</v>
+      </c>
+      <c r="C19" t="s">
         <v>304</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
         <v>37</v>
       </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>7</v>
+      <c r="J19">
+        <v>0</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>393</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>190</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>191</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>175</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>34</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>62.6</v>
       </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>56</v>
       </c>
       <c r="B20" t="s">
+        <v>430</v>
+      </c>
+      <c r="C20" t="s">
         <v>305</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
         <v>37</v>
       </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>7</v>
+      <c r="J20">
+        <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>394</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>192</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>193</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>194</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>34</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>62.6</v>
       </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>57</v>
       </c>
       <c r="B21" t="s">
+        <v>430</v>
+      </c>
+      <c r="C21" t="s">
         <v>305</v>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
         <v>37</v>
       </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>7</v>
+      <c r="J21">
+        <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>395</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>195</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>196</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>194</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>34</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>62.6</v>
       </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>58</v>
       </c>
       <c r="B22" t="s">
+        <v>430</v>
+      </c>
+      <c r="C22" t="s">
         <v>305</v>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
         <v>37</v>
       </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>7</v>
+      <c r="J22">
+        <v>0</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>396</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>197</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>198</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>194</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>34</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>62.6</v>
       </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>59</v>
       </c>
       <c r="B23" t="s">
+        <v>430</v>
+      </c>
+      <c r="C23" t="s">
         <v>305</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
         <v>37</v>
       </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>7</v>
+      <c r="J23">
+        <v>0</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>397</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>199</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>200</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>194</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>34</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>62.6</v>
       </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>60</v>
       </c>
       <c r="B24" t="s">
+        <v>430</v>
+      </c>
+      <c r="C24" t="s">
         <v>305</v>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
         <v>37</v>
       </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>7</v>
+      <c r="J24">
+        <v>0</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>398</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>201</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>202</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>194</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>34</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>62.6</v>
       </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>61</v>
       </c>
       <c r="B25" t="s">
+        <v>430</v>
+      </c>
+      <c r="C25" t="s">
         <v>305</v>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
         <v>37</v>
       </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>7</v>
+      <c r="J25">
+        <v>0</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>399</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>203</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>204</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>194</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>34</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>62.6</v>
       </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>62</v>
       </c>
       <c r="B26" t="s">
+        <v>430</v>
+      </c>
+      <c r="C26" t="s">
         <v>305</v>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
         <v>37</v>
       </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>7</v>
+      <c r="J26">
+        <v>0</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>400</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>205</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>206</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>194</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>34</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>62.6</v>
       </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>63</v>
       </c>
       <c r="B27" t="s">
+        <v>430</v>
+      </c>
+      <c r="C27" t="s">
         <v>305</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
         <v>37</v>
       </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>7</v>
+      <c r="J27">
+        <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>401</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>207</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>208</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>194</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>34</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>62.6</v>
       </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>64</v>
       </c>
       <c r="B28" t="s">
+        <v>430</v>
+      </c>
+      <c r="C28" t="s">
         <v>305</v>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
         <v>37</v>
       </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>7</v>
+      <c r="J28">
+        <v>0</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>402</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>209</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>210</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>194</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>34</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>62.6</v>
       </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>65</v>
       </c>
       <c r="B29" t="s">
+        <v>430</v>
+      </c>
+      <c r="C29" t="s">
         <v>303</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
         <v>37</v>
       </c>
-      <c r="E29">
-        <v>2</v>
-      </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>7</v>
+      <c r="J29">
+        <v>0</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>403</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>211</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>212</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>213</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>34</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>62.6</v>
       </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>66</v>
       </c>
       <c r="B30" t="s">
+        <v>430</v>
+      </c>
+      <c r="C30" t="s">
         <v>303</v>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
         <v>37</v>
       </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>7</v>
+      <c r="J30">
+        <v>0</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>404</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>214</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>215</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>213</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>34</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>62.6</v>
       </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>67</v>
       </c>
       <c r="B31" t="s">
+        <v>429</v>
+      </c>
+      <c r="C31" t="s">
         <v>303</v>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
         <v>37</v>
       </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>7</v>
+      <c r="J31">
+        <v>0</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>405</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>216</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>217</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>213</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>34</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>62.6</v>
       </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>68</v>
       </c>
       <c r="B32" t="s">
+        <v>429</v>
+      </c>
+      <c r="C32" t="s">
         <v>303</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
         <v>37</v>
       </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>7</v>
+      <c r="J32">
+        <v>0</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>406</v>
       </c>
-      <c r="N32" t="s">
+      <c r="O32" t="s">
         <v>218</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>219</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>213</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>34</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>62.6</v>
       </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>69</v>
       </c>
       <c r="B33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C33" t="s">
         <v>303</v>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
         <v>37</v>
       </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>7</v>
+      <c r="J33">
+        <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>407</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>220</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>221</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>213</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>34</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>62.6</v>
       </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>70</v>
       </c>
       <c r="B34" t="s">
+        <v>429</v>
+      </c>
+      <c r="C34" t="s">
         <v>303</v>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
         <v>37</v>
       </c>
-      <c r="E34">
-        <v>2</v>
-      </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>7</v>
+      <c r="J34">
+        <v>0</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>408</v>
       </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>222</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>223</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>213</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>34</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>62.6</v>
       </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>71</v>
       </c>
       <c r="B35" t="s">
+        <v>429</v>
+      </c>
+      <c r="C35" t="s">
         <v>303</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
         <v>37</v>
       </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>7</v>
+      <c r="J35">
+        <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>409</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>224</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>225</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>213</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>34</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>62.6</v>
       </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>72</v>
       </c>
       <c r="B36" t="s">
+        <v>429</v>
+      </c>
+      <c r="C36" t="s">
         <v>303</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
         <v>37</v>
       </c>
-      <c r="E36">
-        <v>2</v>
-      </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>7</v>
+      <c r="J36">
+        <v>0</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M36" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>410</v>
       </c>
-      <c r="N36" t="s">
+      <c r="O36" t="s">
         <v>226</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>227</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>213</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>34</v>
       </c>
-      <c r="R36">
+      <c r="S36">
         <v>62.6</v>
       </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>73</v>
       </c>
       <c r="B37" t="s">
+        <v>429</v>
+      </c>
+      <c r="C37" t="s">
         <v>303</v>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
         <v>37</v>
       </c>
-      <c r="E37">
-        <v>2</v>
-      </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>7</v>
+      <c r="J37">
+        <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>411</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>228</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>229</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>213</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>34</v>
       </c>
-      <c r="R37">
+      <c r="S37">
         <v>62.6</v>
       </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>74</v>
       </c>
       <c r="B38" t="s">
+        <v>429</v>
+      </c>
+      <c r="C38" t="s">
         <v>303</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
         <v>37</v>
       </c>
-      <c r="E38">
-        <v>2</v>
-      </c>
       <c r="F38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>7</v>
+      <c r="J38">
+        <v>0</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M38" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>412</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>230</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>231</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>213</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>34</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>62.6</v>
       </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>75</v>
       </c>
       <c r="B39" t="s">
+        <v>429</v>
+      </c>
+      <c r="C39" t="s">
         <v>303</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
         <v>37</v>
       </c>
-      <c r="E39">
-        <v>2</v>
-      </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>7</v>
+      <c r="J39">
+        <v>0</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>413</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" t="s">
         <v>232</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>233</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>213</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>34</v>
       </c>
-      <c r="R39">
+      <c r="S39">
         <v>62.6</v>
       </c>
-      <c r="S39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>76</v>
       </c>
       <c r="B40" t="s">
+        <v>429</v>
+      </c>
+      <c r="C40" t="s">
         <v>303</v>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
         <v>37</v>
       </c>
-      <c r="E40">
-        <v>2</v>
-      </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>7</v>
+      <c r="J40">
+        <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" t="s">
         <v>414</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>234</v>
       </c>
-      <c r="O40" t="s">
+      <c r="P40" t="s">
         <v>235</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>213</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>34</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <v>62.6</v>
       </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>77</v>
       </c>
       <c r="B41" t="s">
+        <v>429</v>
+      </c>
+      <c r="C41" t="s">
         <v>306</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
         <v>37</v>
       </c>
-      <c r="E41">
-        <v>2</v>
-      </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>7</v>
+      <c r="J41">
+        <v>0</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>415</v>
       </c>
-      <c r="N41" t="s">
+      <c r="O41" t="s">
         <v>236</v>
       </c>
-      <c r="O41" t="s">
+      <c r="P41" t="s">
         <v>237</v>
       </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
         <v>238</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>34</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <v>62.6</v>
       </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>78</v>
       </c>
       <c r="B42" t="s">
+        <v>429</v>
+      </c>
+      <c r="C42" t="s">
         <v>306</v>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
         <v>37</v>
       </c>
-      <c r="E42">
-        <v>2</v>
-      </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>7</v>
+      <c r="J42">
+        <v>0</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M42" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M42" t="s">
+      <c r="N42" t="s">
         <v>416</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
         <v>239</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>240</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>238</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>34</v>
       </c>
-      <c r="R42">
+      <c r="S42">
         <v>62.6</v>
       </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>79</v>
       </c>
       <c r="B43" t="s">
+        <v>429</v>
+      </c>
+      <c r="C43" t="s">
         <v>306</v>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
         <v>37</v>
       </c>
-      <c r="E43">
-        <v>2</v>
-      </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>7</v>
+      <c r="J43">
+        <v>0</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
         <v>417</v>
       </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
         <v>241</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>242</v>
       </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
         <v>238</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>34</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <v>62.6</v>
       </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>80</v>
       </c>
       <c r="B44" t="s">
+        <v>429</v>
+      </c>
+      <c r="C44" t="s">
         <v>306</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
         <v>37</v>
       </c>
-      <c r="E44">
-        <v>2</v>
-      </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>7</v>
+      <c r="J44">
+        <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M44" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>418</v>
       </c>
-      <c r="N44" t="s">
+      <c r="O44" t="s">
         <v>243</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>244</v>
       </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
         <v>238</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>34</v>
       </c>
-      <c r="R44">
+      <c r="S44">
         <v>62.6</v>
       </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>81</v>
       </c>
       <c r="B45" t="s">
+        <v>429</v>
+      </c>
+      <c r="C45" t="s">
         <v>306</v>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
         <v>37</v>
       </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>7</v>
+      <c r="J45">
+        <v>0</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M45" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M45" t="s">
+      <c r="N45" t="s">
         <v>419</v>
       </c>
-      <c r="N45" t="s">
+      <c r="O45" t="s">
         <v>245</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
         <v>246</v>
       </c>
-      <c r="P45" t="s">
+      <c r="Q45" t="s">
         <v>238</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>34</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <v>62.6</v>
       </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" t="s">
+        <v>429</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="2">
-        <v>2</v>
-      </c>
       <c r="F46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
       </c>
-      <c r="H46">
-        <v>0</v>
+      <c r="H46" s="2">
+        <v>1</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>7</v>
+      <c r="J46">
+        <v>0</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="L46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="Q46" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="Q46" s="2" t="s">
+      <c r="R46" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R46" s="2">
+      <c r="S46" s="2">
         <v>62.6</v>
       </c>
-      <c r="S46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" t="s">
+        <v>431</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
         <v>37</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>3</v>
       </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>2</v>
+      <c r="J47">
+        <v>0</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M47" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M47" t="s">
-        <v>338</v>
       </c>
       <c r="N47" t="s">
         <v>338</v>
       </c>
       <c r="O47" t="s">
+        <v>338</v>
+      </c>
+      <c r="P47" t="s">
         <v>339</v>
       </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
         <v>340</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
         <v>341</v>
-      </c>
-      <c r="R47">
-        <v>162.5</v>
       </c>
       <c r="S47">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T47">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" t="s">
+        <v>431</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
         <v>37</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>3</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>2</v>
+      <c r="J48">
+        <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M48" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M48" t="s">
-        <v>342</v>
       </c>
       <c r="N48" t="s">
         <v>342</v>
       </c>
       <c r="O48" t="s">
+        <v>342</v>
+      </c>
+      <c r="P48" t="s">
         <v>339</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>340</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
         <v>341</v>
-      </c>
-      <c r="R48">
-        <v>162.5</v>
       </c>
       <c r="S48">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T48">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>13</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" t="s">
+        <v>431</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
         <v>37</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>3</v>
       </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
       <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <v>0.3</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>2</v>
+      <c r="J49">
+        <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M49" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M49" t="s">
-        <v>343</v>
       </c>
       <c r="N49" t="s">
         <v>343</v>
       </c>
       <c r="O49" t="s">
+        <v>343</v>
+      </c>
+      <c r="P49" t="s">
         <v>339</v>
       </c>
-      <c r="P49" t="s">
+      <c r="Q49" t="s">
         <v>340</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="R49" t="s">
         <v>341</v>
-      </c>
-      <c r="R49">
-        <v>162.5</v>
       </c>
       <c r="S49">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T49">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" t="s">
+        <v>431</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
         <v>37</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>3</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
       <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
         <v>0.1</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>2</v>
+      <c r="J50">
+        <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M50" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M50" t="s">
-        <v>344</v>
       </c>
       <c r="N50" t="s">
         <v>344</v>
       </c>
       <c r="O50" t="s">
+        <v>344</v>
+      </c>
+      <c r="P50" t="s">
         <v>335</v>
       </c>
-      <c r="P50" t="s">
+      <c r="Q50" t="s">
         <v>336</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="R50" t="s">
         <v>337</v>
-      </c>
-      <c r="R50">
-        <v>162.5</v>
       </c>
       <c r="S50">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T50">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" t="s">
+        <v>431</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
         <v>37</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>3</v>
       </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>2</v>
+      <c r="J51">
+        <v>0</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L51" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="M51" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M51" t="s">
-        <v>345</v>
       </c>
       <c r="N51" t="s">
         <v>345</v>
       </c>
       <c r="O51" t="s">
+        <v>345</v>
+      </c>
+      <c r="P51" t="s">
         <v>346</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>347</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
         <v>348</v>
-      </c>
-      <c r="R51">
-        <v>162.5</v>
       </c>
       <c r="S51">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T51">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" t="s">
+        <v>431</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
         <v>37</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>3</v>
       </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>2</v>
+      <c r="J52">
+        <v>0</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M52" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M52" t="s">
-        <v>349</v>
       </c>
       <c r="N52" t="s">
         <v>349</v>
       </c>
       <c r="O52" t="s">
+        <v>349</v>
+      </c>
+      <c r="P52" t="s">
         <v>346</v>
       </c>
-      <c r="P52" t="s">
+      <c r="Q52" t="s">
         <v>347</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="R52" t="s">
         <v>348</v>
-      </c>
-      <c r="R52">
-        <v>162.5</v>
       </c>
       <c r="S52">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T52">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" t="s">
+        <v>431</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C53" s="9">
-        <v>1</v>
-      </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="9">
+        <v>1</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E53" s="9">
+      <c r="F53" s="9">
         <v>3</v>
       </c>
-      <c r="F53" s="9">
-        <v>1</v>
-      </c>
       <c r="G53" s="9">
+        <v>1</v>
+      </c>
+      <c r="H53" s="9">
         <v>0.3</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
       <c r="I53">
         <v>0</v>
       </c>
-      <c r="J53" s="11" t="s">
-        <v>2</v>
+      <c r="J53">
+        <v>0</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>2</v>
       </c>
       <c r="L53" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="M53" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="M53" s="9" t="s">
-        <v>350</v>
       </c>
       <c r="N53" s="9" t="s">
         <v>350</v>
       </c>
       <c r="O53" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="P53" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="P53" s="9" t="s">
+      <c r="Q53" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="Q53" s="9" t="s">
+      <c r="R53" s="9" t="s">
         <v>348</v>
-      </c>
-      <c r="R53" s="9">
-        <v>162.5</v>
       </c>
       <c r="S53" s="9">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T53" s="9">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" t="s">
+        <v>431</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C54" s="6">
-        <v>1</v>
-      </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E54" s="6">
+      <c r="F54" s="6">
         <v>3</v>
       </c>
-      <c r="F54" s="6">
-        <v>1</v>
-      </c>
       <c r="G54" s="6">
+        <v>1</v>
+      </c>
+      <c r="H54" s="6">
         <v>0.1</v>
       </c>
-      <c r="H54">
-        <v>1</v>
-      </c>
       <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>2</v>
       </c>
       <c r="L54" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M54" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>351</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="P54" s="6" t="s">
+      <c r="Q54" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="Q54" s="6" t="s">
+      <c r="R54" s="6" t="s">
         <v>348</v>
-      </c>
-      <c r="R54" s="6">
-        <v>162.5</v>
       </c>
       <c r="S54" s="6">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T54" s="6">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" t="s">
+        <v>431</v>
+      </c>
+      <c r="C55" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="C55" s="17">
-        <v>1</v>
-      </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="17">
+        <v>1</v>
+      </c>
+      <c r="E55" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E55" s="17">
+      <c r="F55" s="17">
         <v>3</v>
       </c>
-      <c r="F55" s="17">
-        <v>1</v>
-      </c>
       <c r="G55" s="17">
         <v>1</v>
       </c>
@@ -5391,904 +5577,949 @@
         <v>1</v>
       </c>
       <c r="I55" s="17">
-        <v>0</v>
-      </c>
-      <c r="J55" s="19" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J55" s="17">
+        <v>0</v>
       </c>
       <c r="K55" s="19" t="s">
         <v>2</v>
       </c>
       <c r="L55" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="M55" s="19" t="s">
         <v>9</v>
-      </c>
-      <c r="M55" s="17" t="s">
-        <v>427</v>
       </c>
       <c r="N55" s="17" t="s">
         <v>427</v>
       </c>
       <c r="O55" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="P55" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="P55" s="17" t="s">
+      <c r="Q55" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="Q55" s="17" t="s">
+      <c r="R55" s="17" t="s">
         <v>375</v>
-      </c>
-      <c r="R55" s="17">
-        <v>162.5</v>
       </c>
       <c r="S55" s="17">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T55" s="17">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" t="s">
+        <v>431</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C56" s="6">
-        <v>1</v>
-      </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="6">
+        <v>1</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E56" s="6">
+      <c r="F56" s="6">
         <v>3</v>
       </c>
-      <c r="F56" s="6">
-        <v>1</v>
-      </c>
       <c r="G56" s="6">
+        <v>1</v>
+      </c>
+      <c r="H56" s="6">
         <v>0.1</v>
       </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
       <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>2</v>
       </c>
       <c r="L56" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M56" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>372</v>
       </c>
       <c r="N56" s="6" t="s">
         <v>372</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="P56" s="6" t="s">
+      <c r="Q56" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="Q56" s="6" t="s">
+      <c r="R56" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="R56" s="6">
-        <v>162.5</v>
       </c>
       <c r="S56" s="6">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T56" s="6">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" t="s">
+        <v>431</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C57" s="6">
-        <v>1</v>
-      </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="6">
+        <v>1</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E57" s="6">
+      <c r="F57" s="6">
         <v>3</v>
       </c>
-      <c r="F57" s="6">
-        <v>1</v>
-      </c>
       <c r="G57" s="6">
+        <v>1</v>
+      </c>
+      <c r="H57" s="6">
         <v>0.1</v>
       </c>
-      <c r="H57">
-        <v>1</v>
-      </c>
       <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
       </c>
       <c r="K57" s="8" t="s">
         <v>2</v>
       </c>
       <c r="L57" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M57" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>367</v>
       </c>
       <c r="O57" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="P57" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="P57" s="6" t="s">
+      <c r="Q57" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="Q57" s="6" t="s">
+      <c r="R57" s="6" t="s">
         <v>370</v>
-      </c>
-      <c r="R57" s="6">
-        <v>162.5</v>
       </c>
       <c r="S57" s="6">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="6">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" t="s">
+        <v>431</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
         <v>37</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>3</v>
       </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58">
         <v>0</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>2</v>
+      <c r="J58">
+        <v>0</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M58" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M58" t="s">
-        <v>352</v>
       </c>
       <c r="N58" t="s">
         <v>352</v>
       </c>
       <c r="O58" t="s">
+        <v>352</v>
+      </c>
+      <c r="P58" t="s">
         <v>353</v>
       </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
         <v>354</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="R58" t="s">
         <v>355</v>
-      </c>
-      <c r="R58">
-        <v>162.5</v>
       </c>
       <c r="S58">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T58">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" t="s">
+        <v>431</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
         <v>37</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>3</v>
       </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>2</v>
+      <c r="J59">
+        <v>0</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M59" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M59" t="s">
-        <v>356</v>
       </c>
       <c r="N59" t="s">
         <v>356</v>
       </c>
       <c r="O59" t="s">
+        <v>356</v>
+      </c>
+      <c r="P59" t="s">
         <v>353</v>
       </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
         <v>354</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="R59" t="s">
         <v>355</v>
-      </c>
-      <c r="R59">
-        <v>162.5</v>
       </c>
       <c r="S59">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T59">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" t="s">
+        <v>431</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
         <v>37</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>3</v>
       </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
       <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
         <v>0.3</v>
       </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
       <c r="I60">
         <v>0</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>2</v>
+      <c r="J60">
+        <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M60" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M60" t="s">
-        <v>357</v>
       </c>
       <c r="N60" t="s">
         <v>357</v>
       </c>
       <c r="O60" t="s">
+        <v>357</v>
+      </c>
+      <c r="P60" t="s">
         <v>353</v>
       </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
         <v>354</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="R60" t="s">
         <v>355</v>
-      </c>
-      <c r="R60">
-        <v>162.5</v>
       </c>
       <c r="S60">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T60">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" t="s">
+        <v>431</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C61" s="2">
-        <v>1</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="2">
+        <v>1</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="2">
+      <c r="F61" s="2">
         <v>3</v>
       </c>
-      <c r="F61" s="2">
-        <v>1</v>
-      </c>
       <c r="G61" s="2">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2">
         <v>0.1</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
       <c r="I61">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="s">
-        <v>2</v>
+      <c r="J61">
+        <v>0</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>2</v>
       </c>
       <c r="L61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M61" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>358</v>
       </c>
       <c r="O61" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P61" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="P61" s="2" t="s">
+      <c r="Q61" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="Q61" s="2" t="s">
+      <c r="R61" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="R61" s="2">
-        <v>162.5</v>
       </c>
       <c r="S61" s="2">
         <v>162.5</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="2">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>15</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" t="s">
+        <v>431</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
         <v>37</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>3</v>
       </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>4</v>
+      <c r="J62">
+        <v>0</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>4</v>
       </c>
       <c r="L62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M62" t="s">
-        <v>359</v>
       </c>
       <c r="N62" t="s">
         <v>359</v>
       </c>
       <c r="O62" t="s">
+        <v>359</v>
+      </c>
+      <c r="P62" t="s">
         <v>360</v>
       </c>
-      <c r="P62" t="s">
+      <c r="Q62" t="s">
         <v>361</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="R62" t="s">
         <v>362</v>
       </c>
-      <c r="R62">
+      <c r="S62">
         <v>92.6</v>
       </c>
-      <c r="S62">
+      <c r="T62">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" t="s">
+        <v>431</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C63" s="2">
-        <v>1</v>
-      </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="2">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E63" s="2">
+      <c r="F63" s="2">
         <v>3</v>
       </c>
-      <c r="F63" s="2">
-        <v>1</v>
-      </c>
       <c r="G63" s="2">
         <v>1</v>
       </c>
-      <c r="H63">
-        <v>0</v>
+      <c r="H63" s="2">
+        <v>1</v>
       </c>
       <c r="I63">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>4</v>
+      <c r="J63">
+        <v>0</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L63" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M63" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>363</v>
       </c>
       <c r="O63" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="P63" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="P63" s="2" t="s">
+      <c r="Q63" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="Q63" s="2" t="s">
+      <c r="R63" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="R63" s="2">
+      <c r="S63" s="2">
         <v>92.6</v>
       </c>
-      <c r="S63" s="2">
+      <c r="T63" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="64" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C64" s="12">
-        <v>1</v>
-      </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="12">
+        <v>1</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E64" s="12">
+      <c r="F64" s="12">
         <v>3</v>
       </c>
-      <c r="F64" s="12">
-        <v>1</v>
-      </c>
       <c r="G64" s="12">
         <v>1</v>
       </c>
       <c r="H64" s="12">
         <v>1</v>
       </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>334</v>
+      <c r="I64" s="12">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
       </c>
       <c r="K64" s="8" t="s">
         <v>334</v>
       </c>
       <c r="L64" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="M64" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="M64" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="N64" s="12" t="s">
         <v>115</v>
       </c>
       <c r="O64" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="P64" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="P64" s="12" t="s">
+      <c r="Q64" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="Q64" s="12" t="s">
+      <c r="R64" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="R64" s="12">
+      <c r="S64" s="12">
         <v>25</v>
       </c>
-      <c r="S64" s="12">
+      <c r="T64" s="12">
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C65" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="C65" s="13">
-        <v>1</v>
-      </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="13">
+        <v>1</v>
+      </c>
+      <c r="E65" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E65" s="13">
+      <c r="F65" s="13">
         <v>3</v>
       </c>
-      <c r="F65" s="13">
-        <v>1</v>
-      </c>
       <c r="G65" s="13">
         <v>1</v>
       </c>
-      <c r="H65" s="12">
-        <v>1</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65" s="8" t="s">
-        <v>334</v>
+      <c r="H65" s="13">
+        <v>1</v>
+      </c>
+      <c r="I65" s="12">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
       </c>
       <c r="K65" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="L65" s="15" t="s">
+      <c r="L65" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="M65" s="15" t="s">
         <v>9</v>
-      </c>
-      <c r="M65" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="N65" s="13" t="s">
         <v>118</v>
       </c>
       <c r="O65" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="P65" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="P65" s="13" t="s">
+      <c r="Q65" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="Q65" s="13" t="s">
+      <c r="R65" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="R65" s="13">
+      <c r="S65" s="13">
         <v>25</v>
       </c>
-      <c r="S65" s="13">
+      <c r="T65" s="13">
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>85</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
         <v>36</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>3</v>
       </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>4</v>
+      <c r="J66">
+        <v>0</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>4</v>
       </c>
       <c r="L66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M66" t="s">
-        <v>121</v>
       </c>
       <c r="N66" t="s">
         <v>121</v>
       </c>
-      <c r="O66" s="1" t="s">
+      <c r="O66" t="s">
+        <v>121</v>
+      </c>
+      <c r="P66" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P66" t="s">
+      <c r="Q66" t="s">
         <v>122</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>123</v>
       </c>
-      <c r="R66">
+      <c r="S66">
         <v>92.6</v>
       </c>
-      <c r="S66">
+      <c r="T66">
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C67" s="2">
-        <v>1</v>
-      </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="2">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E67" s="2">
+      <c r="F67" s="2">
         <v>3</v>
       </c>
-      <c r="F67" s="2">
-        <v>1</v>
-      </c>
       <c r="G67" s="2">
         <v>1</v>
       </c>
-      <c r="H67">
-        <v>0</v>
+      <c r="H67" s="2">
+        <v>1</v>
       </c>
       <c r="I67">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>4</v>
+      <c r="J67">
+        <v>0</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L67" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M67" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="O67" s="3" t="s">
+      <c r="O67" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P67" s="2" t="s">
+      <c r="Q67" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Q67" s="2" t="s">
+      <c r="R67" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="R67" s="2">
+      <c r="S67" s="2">
         <v>92.6</v>
       </c>
-      <c r="S67" s="2">
+      <c r="T67" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
         <v>37</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>3</v>
       </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>6</v>
+      <c r="J68">
+        <v>0</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M68" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M68" t="s">
-        <v>127</v>
       </c>
       <c r="N68" t="s">
         <v>127</v>
       </c>
       <c r="O68" t="s">
+        <v>127</v>
+      </c>
+      <c r="P68" t="s">
         <v>128</v>
       </c>
-      <c r="P68" t="s">
+      <c r="Q68" t="s">
         <v>129</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
         <v>34</v>
       </c>
-      <c r="R68">
+      <c r="S68">
         <v>25</v>
       </c>
-      <c r="S68">
+      <c r="T68">
         <v>160</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
         <v>37</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>3</v>
       </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>6</v>
+      <c r="J69">
+        <v>0</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M69" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M69" t="s">
-        <v>127</v>
       </c>
       <c r="N69" t="s">
         <v>127</v>
       </c>
       <c r="O69" t="s">
+        <v>127</v>
+      </c>
+      <c r="P69" t="s">
         <v>128</v>
       </c>
-      <c r="P69" t="s">
+      <c r="Q69" t="s">
         <v>130</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="R69" t="s">
         <v>34</v>
       </c>
-      <c r="R69">
+      <c r="S69">
         <v>25</v>
       </c>
-      <c r="S69">
+      <c r="T69">
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
         <v>37</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>3</v>
       </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>0</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>6</v>
+      <c r="J70">
+        <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M70" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M70" t="s">
-        <v>131</v>
       </c>
       <c r="N70" t="s">
         <v>131</v>
@@ -6297,57 +6528,60 @@
         <v>131</v>
       </c>
       <c r="P70" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q70" t="s">
         <v>132</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="R70" t="s">
         <v>34</v>
       </c>
-      <c r="R70">
+      <c r="S70">
         <v>25</v>
       </c>
-      <c r="S70">
+      <c r="T70">
         <v>160</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>89</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
         <v>37</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>3</v>
       </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71">
         <v>0</v>
       </c>
-      <c r="J71" s="1" t="s">
-        <v>6</v>
+      <c r="J71">
+        <v>0</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M71" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M71" t="s">
-        <v>133</v>
       </c>
       <c r="N71" t="s">
         <v>133</v>
@@ -6356,57 +6590,60 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q71" t="s">
         <v>134</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R71" t="s">
         <v>34</v>
       </c>
-      <c r="R71">
+      <c r="S71">
         <v>25</v>
       </c>
-      <c r="S71">
+      <c r="T71">
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>90</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
         <v>37</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>3</v>
       </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
       </c>
-      <c r="J72" s="1" t="s">
-        <v>6</v>
+      <c r="J72">
+        <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M72" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M72" t="s">
-        <v>135</v>
       </c>
       <c r="N72" t="s">
         <v>135</v>
@@ -6415,57 +6652,60 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q72" t="s">
         <v>136</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="R72" t="s">
         <v>34</v>
       </c>
-      <c r="R72">
+      <c r="S72">
         <v>25</v>
       </c>
-      <c r="S72">
+      <c r="T72">
         <v>160</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>91</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
         <v>37</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>3</v>
       </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>6</v>
+      <c r="J73">
+        <v>0</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M73" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M73" t="s">
-        <v>137</v>
       </c>
       <c r="N73" t="s">
         <v>137</v>
@@ -6474,57 +6714,60 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q73" t="s">
         <v>138</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="R73" t="s">
         <v>34</v>
       </c>
-      <c r="R73">
+      <c r="S73">
         <v>25</v>
       </c>
-      <c r="S73">
+      <c r="T73">
         <v>160</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>92</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
         <v>37</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>3</v>
       </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>6</v>
+      <c r="J74">
+        <v>0</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M74" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M74" t="s">
-        <v>139</v>
       </c>
       <c r="N74" t="s">
         <v>139</v>
@@ -6533,57 +6776,60 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q74" t="s">
         <v>140</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="R74" t="s">
         <v>34</v>
       </c>
-      <c r="R74">
+      <c r="S74">
         <v>25</v>
       </c>
-      <c r="S74">
+      <c r="T74">
         <v>160</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>93</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
         <v>37</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>3</v>
       </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>0</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>6</v>
+      <c r="J75">
+        <v>0</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M75" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M75" t="s">
-        <v>141</v>
       </c>
       <c r="N75" t="s">
         <v>141</v>
@@ -6592,57 +6838,60 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q75" t="s">
         <v>142</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R75" t="s">
         <v>34</v>
       </c>
-      <c r="R75">
+      <c r="S75">
         <v>25</v>
       </c>
-      <c r="S75">
+      <c r="T75">
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>94</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
         <v>37</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>3</v>
       </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76">
         <v>0</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>6</v>
+      <c r="J76">
+        <v>0</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M76" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M76" t="s">
-        <v>143</v>
       </c>
       <c r="N76" t="s">
         <v>143</v>
@@ -6651,57 +6900,60 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q76" t="s">
         <v>144</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="R76" t="s">
         <v>34</v>
       </c>
-      <c r="R76">
+      <c r="S76">
         <v>25</v>
       </c>
-      <c r="S76">
+      <c r="T76">
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
         <v>37</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>3</v>
       </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>0</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>6</v>
+      <c r="J77">
+        <v>0</v>
       </c>
       <c r="K77" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M77" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M77" t="s">
-        <v>145</v>
       </c>
       <c r="N77" t="s">
         <v>145</v>
@@ -6710,57 +6962,60 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q77" t="s">
         <v>146</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="R77" t="s">
         <v>34</v>
       </c>
-      <c r="R77">
+      <c r="S77">
         <v>25</v>
       </c>
-      <c r="S77">
+      <c r="T77">
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C78" s="2">
-        <v>1</v>
-      </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="2">
+        <v>1</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E78" s="2">
+      <c r="F78" s="2">
         <v>3</v>
       </c>
-      <c r="F78" s="2">
-        <v>1</v>
-      </c>
       <c r="G78" s="2">
         <v>1</v>
       </c>
-      <c r="H78">
-        <v>0</v>
+      <c r="H78" s="2">
+        <v>1</v>
       </c>
       <c r="I78">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="s">
-        <v>6</v>
+      <c r="J78">
+        <v>0</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>6</v>
       </c>
       <c r="L78" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M78" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>147</v>
@@ -6769,2079 +7024,2178 @@
         <v>147</v>
       </c>
       <c r="P78" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q78" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="Q78" s="2" t="s">
+      <c r="R78" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R78" s="2">
+      <c r="S78" s="2">
         <v>25</v>
       </c>
-      <c r="S78" s="2">
+      <c r="T78" s="2">
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>99</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
         <v>98</v>
       </c>
-      <c r="E79">
-        <v>2</v>
-      </c>
       <c r="F79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79">
         <v>0</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>7</v>
+      <c r="J79">
+        <v>0</v>
       </c>
       <c r="K79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L79" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M79" t="s">
-        <v>149</v>
       </c>
       <c r="N79" t="s">
         <v>149</v>
       </c>
       <c r="O79" t="s">
+        <v>149</v>
+      </c>
+      <c r="P79" t="s">
         <v>150</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>151</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="R79" t="s">
         <v>34</v>
       </c>
-      <c r="R79">
+      <c r="S79">
         <v>60.4</v>
       </c>
-      <c r="S79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>100</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
         <v>98</v>
       </c>
-      <c r="E80">
-        <v>2</v>
-      </c>
       <c r="F80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>0</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>7</v>
+      <c r="J80">
+        <v>0</v>
       </c>
       <c r="K80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L80" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M80" t="s">
-        <v>152</v>
       </c>
       <c r="N80" t="s">
         <v>152</v>
       </c>
       <c r="O80" t="s">
+        <v>152</v>
+      </c>
+      <c r="P80" t="s">
         <v>150</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>151</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="R80" t="s">
         <v>34</v>
       </c>
-      <c r="R80">
+      <c r="S80">
         <v>60.4</v>
       </c>
-      <c r="S80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>101</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
         <v>98</v>
       </c>
-      <c r="E81">
-        <v>2</v>
-      </c>
       <c r="F81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81">
         <v>0</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>7</v>
+      <c r="J81">
+        <v>0</v>
       </c>
       <c r="K81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L81" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L81" s="1" t="s">
+      <c r="M81" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M81" t="s">
-        <v>153</v>
       </c>
       <c r="N81" t="s">
         <v>153</v>
       </c>
       <c r="O81" t="s">
+        <v>153</v>
+      </c>
+      <c r="P81" t="s">
         <v>150</v>
       </c>
-      <c r="P81" t="s">
+      <c r="Q81" t="s">
         <v>151</v>
       </c>
-      <c r="Q81" t="s">
+      <c r="R81" t="s">
         <v>34</v>
       </c>
-      <c r="R81">
+      <c r="S81">
         <v>60.4</v>
       </c>
-      <c r="S81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>102</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
         <v>98</v>
       </c>
-      <c r="E82">
-        <v>2</v>
-      </c>
       <c r="F82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82">
         <v>0</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>7</v>
+      <c r="J82">
+        <v>0</v>
       </c>
       <c r="K82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L82" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L82" s="1" t="s">
+      <c r="M82" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M82" t="s">
-        <v>257</v>
       </c>
       <c r="N82" t="s">
         <v>257</v>
       </c>
       <c r="O82" t="s">
+        <v>257</v>
+      </c>
+      <c r="P82" t="s">
         <v>275</v>
       </c>
-      <c r="P82" t="s">
+      <c r="Q82" t="s">
         <v>280</v>
       </c>
-      <c r="Q82" t="s">
+      <c r="R82" t="s">
         <v>34</v>
       </c>
-      <c r="R82">
+      <c r="S82">
         <v>60.4</v>
       </c>
-      <c r="S82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>103</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
         <v>98</v>
       </c>
-      <c r="E83">
-        <v>2</v>
-      </c>
       <c r="F83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83">
         <v>1</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83">
         <v>0</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>7</v>
+      <c r="J83">
+        <v>0</v>
       </c>
       <c r="K83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L83" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L83" s="1" t="s">
+      <c r="M83" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M83" t="s">
-        <v>258</v>
       </c>
       <c r="N83" t="s">
         <v>258</v>
       </c>
       <c r="O83" t="s">
+        <v>258</v>
+      </c>
+      <c r="P83" t="s">
         <v>275</v>
       </c>
-      <c r="P83" t="s">
+      <c r="Q83" t="s">
         <v>280</v>
       </c>
-      <c r="Q83" t="s">
+      <c r="R83" t="s">
         <v>34</v>
       </c>
-      <c r="R83">
+      <c r="S83">
         <v>60.4</v>
       </c>
-      <c r="S83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>104</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84" t="s">
         <v>98</v>
       </c>
-      <c r="E84">
-        <v>2</v>
-      </c>
       <c r="F84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84">
         <v>1</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84">
         <v>0</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>7</v>
+      <c r="J84">
+        <v>0</v>
       </c>
       <c r="K84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L84" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L84" s="1" t="s">
+      <c r="M84" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M84" t="s">
-        <v>259</v>
       </c>
       <c r="N84" t="s">
         <v>259</v>
       </c>
       <c r="O84" t="s">
+        <v>259</v>
+      </c>
+      <c r="P84" t="s">
         <v>275</v>
       </c>
-      <c r="P84" t="s">
+      <c r="Q84" t="s">
         <v>280</v>
       </c>
-      <c r="Q84" t="s">
+      <c r="R84" t="s">
         <v>34</v>
       </c>
-      <c r="R84">
+      <c r="S84">
         <v>60.4</v>
       </c>
-      <c r="S84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>105</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
         <v>98</v>
       </c>
-      <c r="E85">
-        <v>2</v>
-      </c>
       <c r="F85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85">
         <v>0</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>7</v>
+      <c r="J85">
+        <v>0</v>
       </c>
       <c r="K85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L85" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L85" s="1" t="s">
+      <c r="M85" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M85" t="s">
-        <v>260</v>
       </c>
       <c r="N85" t="s">
         <v>260</v>
       </c>
       <c r="O85" t="s">
+        <v>260</v>
+      </c>
+      <c r="P85" t="s">
         <v>276</v>
       </c>
-      <c r="P85" t="s">
+      <c r="Q85" t="s">
         <v>281</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="R85" t="s">
         <v>34</v>
       </c>
-      <c r="R85">
+      <c r="S85">
         <v>60.4</v>
       </c>
-      <c r="S85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>106</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
         <v>98</v>
       </c>
-      <c r="E86">
-        <v>2</v>
-      </c>
       <c r="F86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86">
         <v>1</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>0</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>7</v>
+      <c r="J86">
+        <v>0</v>
       </c>
       <c r="K86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L86" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L86" s="1" t="s">
+      <c r="M86" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M86" t="s">
-        <v>261</v>
       </c>
       <c r="N86" t="s">
         <v>261</v>
       </c>
       <c r="O86" t="s">
+        <v>261</v>
+      </c>
+      <c r="P86" t="s">
         <v>276</v>
       </c>
-      <c r="P86" t="s">
+      <c r="Q86" t="s">
         <v>281</v>
       </c>
-      <c r="Q86" t="s">
+      <c r="R86" t="s">
         <v>34</v>
       </c>
-      <c r="R86">
+      <c r="S86">
         <v>60.4</v>
       </c>
-      <c r="S86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>107</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87" t="s">
         <v>98</v>
       </c>
-      <c r="E87">
-        <v>2</v>
-      </c>
       <c r="F87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87">
         <v>1</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87">
         <v>0</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>7</v>
+      <c r="J87">
+        <v>0</v>
       </c>
       <c r="K87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L87" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L87" s="1" t="s">
+      <c r="M87" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M87" t="s">
-        <v>262</v>
       </c>
       <c r="N87" t="s">
         <v>262</v>
       </c>
       <c r="O87" t="s">
+        <v>262</v>
+      </c>
+      <c r="P87" t="s">
         <v>276</v>
       </c>
-      <c r="P87" t="s">
+      <c r="Q87" t="s">
         <v>281</v>
       </c>
-      <c r="Q87" t="s">
+      <c r="R87" t="s">
         <v>34</v>
       </c>
-      <c r="R87">
+      <c r="S87">
         <v>60.4</v>
       </c>
-      <c r="S87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>272</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
         <v>98</v>
       </c>
-      <c r="E88">
-        <v>2</v>
-      </c>
       <c r="F88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>7</v>
+      <c r="J88">
+        <v>0</v>
       </c>
       <c r="K88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L88" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L88" s="1" t="s">
+      <c r="M88" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M88" t="s">
-        <v>263</v>
       </c>
       <c r="N88" t="s">
         <v>263</v>
       </c>
       <c r="O88" t="s">
+        <v>263</v>
+      </c>
+      <c r="P88" t="s">
         <v>277</v>
       </c>
-      <c r="P88" t="s">
+      <c r="Q88" t="s">
         <v>282</v>
       </c>
-      <c r="Q88" t="s">
+      <c r="R88" t="s">
         <v>34</v>
       </c>
-      <c r="R88">
+      <c r="S88">
         <v>60.4</v>
       </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>273</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89" t="s">
         <v>98</v>
       </c>
-      <c r="E89">
-        <v>2</v>
-      </c>
       <c r="F89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>7</v>
+      <c r="J89">
+        <v>0</v>
       </c>
       <c r="K89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L89" s="1" t="s">
+      <c r="M89" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M89" t="s">
-        <v>264</v>
       </c>
       <c r="N89" t="s">
         <v>264</v>
       </c>
       <c r="O89" t="s">
+        <v>264</v>
+      </c>
+      <c r="P89" t="s">
         <v>277</v>
       </c>
-      <c r="P89" t="s">
+      <c r="Q89" t="s">
         <v>282</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="R89" t="s">
         <v>34</v>
       </c>
-      <c r="R89">
+      <c r="S89">
         <v>60.4</v>
       </c>
-      <c r="S89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>274</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90" t="s">
         <v>98</v>
       </c>
-      <c r="E90">
-        <v>2</v>
-      </c>
       <c r="F90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90">
         <v>1</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90">
         <v>0</v>
       </c>
-      <c r="J90" s="1" t="s">
-        <v>7</v>
+      <c r="J90">
+        <v>0</v>
       </c>
       <c r="K90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L90" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L90" s="1" t="s">
+      <c r="M90" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M90" t="s">
-        <v>265</v>
       </c>
       <c r="N90" t="s">
         <v>265</v>
       </c>
       <c r="O90" t="s">
+        <v>265</v>
+      </c>
+      <c r="P90" t="s">
         <v>277</v>
       </c>
-      <c r="P90" t="s">
+      <c r="Q90" t="s">
         <v>282</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="R90" t="s">
         <v>34</v>
       </c>
-      <c r="R90">
+      <c r="S90">
         <v>60.4</v>
       </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>108</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
         <v>98</v>
       </c>
-      <c r="E91">
-        <v>2</v>
-      </c>
       <c r="F91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91">
         <v>1</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91">
         <v>0</v>
       </c>
-      <c r="J91" s="1" t="s">
-        <v>7</v>
+      <c r="J91">
+        <v>0</v>
       </c>
       <c r="K91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L91" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L91" s="1" t="s">
+      <c r="M91" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M91" t="s">
-        <v>266</v>
       </c>
       <c r="N91" t="s">
         <v>266</v>
       </c>
       <c r="O91" t="s">
+        <v>266</v>
+      </c>
+      <c r="P91" t="s">
         <v>278</v>
       </c>
-      <c r="P91" t="s">
+      <c r="Q91" t="s">
         <v>283</v>
       </c>
-      <c r="Q91" t="s">
+      <c r="R91" t="s">
         <v>34</v>
       </c>
-      <c r="R91">
+      <c r="S91">
         <v>60.4</v>
       </c>
-      <c r="S91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>109</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92" t="s">
         <v>98</v>
       </c>
-      <c r="E92">
-        <v>2</v>
-      </c>
       <c r="F92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92">
         <v>1</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92">
         <v>0</v>
       </c>
-      <c r="J92" s="1" t="s">
-        <v>7</v>
+      <c r="J92">
+        <v>0</v>
       </c>
       <c r="K92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L92" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L92" s="1" t="s">
+      <c r="M92" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M92" t="s">
-        <v>267</v>
       </c>
       <c r="N92" t="s">
         <v>267</v>
       </c>
       <c r="O92" t="s">
+        <v>267</v>
+      </c>
+      <c r="P92" t="s">
         <v>278</v>
       </c>
-      <c r="P92" t="s">
+      <c r="Q92" t="s">
         <v>283</v>
       </c>
-      <c r="Q92" t="s">
+      <c r="R92" t="s">
         <v>34</v>
       </c>
-      <c r="R92">
+      <c r="S92">
         <v>60.4</v>
       </c>
-      <c r="S92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>110</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93" t="s">
         <v>98</v>
       </c>
-      <c r="E93">
-        <v>2</v>
-      </c>
       <c r="F93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93">
         <v>1</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93">
         <v>0</v>
       </c>
-      <c r="J93" s="1" t="s">
-        <v>7</v>
+      <c r="J93">
+        <v>0</v>
       </c>
       <c r="K93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L93" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L93" s="1" t="s">
+      <c r="M93" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M93" t="s">
-        <v>268</v>
       </c>
       <c r="N93" t="s">
         <v>268</v>
       </c>
       <c r="O93" t="s">
+        <v>268</v>
+      </c>
+      <c r="P93" t="s">
         <v>278</v>
       </c>
-      <c r="P93" t="s">
+      <c r="Q93" t="s">
         <v>283</v>
       </c>
-      <c r="Q93" t="s">
+      <c r="R93" t="s">
         <v>34</v>
       </c>
-      <c r="R93">
+      <c r="S93">
         <v>60.4</v>
       </c>
-      <c r="S93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>111</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
         <v>98</v>
       </c>
-      <c r="E94">
-        <v>2</v>
-      </c>
       <c r="F94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94">
         <v>1</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94">
         <v>0</v>
       </c>
-      <c r="J94" s="1" t="s">
-        <v>7</v>
+      <c r="J94">
+        <v>0</v>
       </c>
       <c r="K94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L94" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L94" s="1" t="s">
+      <c r="M94" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M94" t="s">
-        <v>269</v>
       </c>
       <c r="N94" t="s">
         <v>269</v>
       </c>
       <c r="O94" t="s">
+        <v>269</v>
+      </c>
+      <c r="P94" t="s">
         <v>279</v>
       </c>
-      <c r="P94" t="s">
+      <c r="Q94" t="s">
         <v>284</v>
       </c>
-      <c r="Q94" t="s">
+      <c r="R94" t="s">
         <v>34</v>
       </c>
-      <c r="R94">
+      <c r="S94">
         <v>60.4</v>
       </c>
-      <c r="S94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>112</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
         <v>98</v>
       </c>
-      <c r="E95">
-        <v>2</v>
-      </c>
       <c r="F95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95">
         <v>0</v>
       </c>
-      <c r="J95" s="1" t="s">
-        <v>7</v>
+      <c r="J95">
+        <v>0</v>
       </c>
       <c r="K95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L95" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L95" s="1" t="s">
+      <c r="M95" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M95" t="s">
-        <v>270</v>
       </c>
       <c r="N95" t="s">
         <v>270</v>
       </c>
       <c r="O95" t="s">
+        <v>270</v>
+      </c>
+      <c r="P95" t="s">
         <v>279</v>
       </c>
-      <c r="P95" t="s">
+      <c r="Q95" t="s">
         <v>284</v>
       </c>
-      <c r="Q95" t="s">
+      <c r="R95" t="s">
         <v>34</v>
       </c>
-      <c r="R95">
+      <c r="S95">
         <v>60.4</v>
       </c>
-      <c r="S95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C96" s="2">
-        <v>1</v>
-      </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="2">
+        <v>1</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E96" s="2">
-        <v>2</v>
-      </c>
       <c r="F96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
-      <c r="H96">
-        <v>0</v>
+      <c r="H96" s="2">
+        <v>1</v>
       </c>
       <c r="I96">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>7</v>
+      <c r="J96">
+        <v>0</v>
       </c>
       <c r="K96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>271</v>
       </c>
       <c r="O96" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="P96" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="P96" s="2" t="s">
+      <c r="Q96" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="Q96" s="2" t="s">
+      <c r="R96" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R96" s="2">
+      <c r="S96" s="2">
         <v>60.4</v>
       </c>
-      <c r="S96" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>251</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
         <v>98</v>
       </c>
-      <c r="E97">
-        <v>2</v>
-      </c>
       <c r="F97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97">
         <v>1</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97">
         <v>0</v>
       </c>
-      <c r="J97" s="1" t="s">
-        <v>7</v>
+      <c r="J97">
+        <v>0</v>
       </c>
       <c r="K97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L97" s="1" t="s">
+      <c r="M97" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M97" t="s">
-        <v>253</v>
       </c>
       <c r="N97" t="s">
         <v>253</v>
       </c>
       <c r="O97" t="s">
+        <v>253</v>
+      </c>
+      <c r="P97" t="s">
         <v>254</v>
       </c>
-      <c r="P97" t="s">
+      <c r="Q97" t="s">
         <v>249</v>
       </c>
-      <c r="Q97" t="s">
+      <c r="R97" t="s">
         <v>34</v>
       </c>
-      <c r="R97">
+      <c r="S97">
         <v>80</v>
       </c>
-      <c r="S97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C98" s="2">
-        <v>1</v>
-      </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="2">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E98" s="2">
-        <v>2</v>
-      </c>
       <c r="F98" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
       </c>
-      <c r="H98">
-        <v>0</v>
+      <c r="H98" s="2">
+        <v>1</v>
       </c>
       <c r="I98">
         <v>0</v>
       </c>
-      <c r="J98" s="3" t="s">
-        <v>7</v>
+      <c r="J98">
+        <v>0</v>
       </c>
       <c r="K98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L98" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L98" s="3" t="s">
+      <c r="M98" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>255</v>
       </c>
       <c r="O98" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="P98" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="P98" s="2" t="s">
+      <c r="Q98" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="Q98" s="2" t="s">
+      <c r="R98" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R98" s="2">
+      <c r="S98" s="2">
         <v>80</v>
       </c>
-      <c r="S98" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>285</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C99" t="s">
         <v>302</v>
       </c>
-      <c r="C99" s="4">
-        <v>1</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="D99" s="4">
+        <v>1</v>
+      </c>
+      <c r="E99" t="s">
         <v>98</v>
       </c>
-      <c r="E99" s="4">
-        <v>2</v>
-      </c>
       <c r="F99" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" s="4">
         <v>1</v>
       </c>
-      <c r="H99">
-        <v>0</v>
+      <c r="H99" s="4">
+        <v>1</v>
       </c>
       <c r="I99">
         <v>0</v>
       </c>
-      <c r="J99" s="1" t="s">
-        <v>7</v>
+      <c r="J99">
+        <v>0</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M99" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M99" t="s">
-        <v>291</v>
       </c>
       <c r="N99" t="s">
         <v>291</v>
       </c>
       <c r="O99" t="s">
+        <v>291</v>
+      </c>
+      <c r="P99" t="s">
         <v>292</v>
       </c>
-      <c r="P99" t="s">
+      <c r="Q99" t="s">
         <v>300</v>
       </c>
-      <c r="Q99" t="s">
+      <c r="R99" t="s">
         <v>34</v>
       </c>
-      <c r="R99" s="4">
+      <c r="S99" s="4">
         <v>100</v>
       </c>
-      <c r="S99" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>286</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C100" t="s">
         <v>302</v>
       </c>
-      <c r="C100" s="4">
-        <v>1</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="D100" s="4">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
         <v>98</v>
       </c>
-      <c r="E100" s="4">
-        <v>2</v>
-      </c>
       <c r="F100" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G100" s="4">
         <v>1</v>
       </c>
-      <c r="H100">
-        <v>0</v>
+      <c r="H100" s="4">
+        <v>1</v>
       </c>
       <c r="I100">
         <v>0</v>
       </c>
-      <c r="J100" s="1" t="s">
-        <v>7</v>
+      <c r="J100">
+        <v>0</v>
       </c>
       <c r="K100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M100" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M100" t="s">
-        <v>293</v>
       </c>
       <c r="N100" t="s">
         <v>293</v>
       </c>
       <c r="O100" t="s">
+        <v>293</v>
+      </c>
+      <c r="P100" t="s">
         <v>292</v>
       </c>
-      <c r="P100" t="s">
+      <c r="Q100" t="s">
         <v>300</v>
       </c>
-      <c r="Q100" t="s">
+      <c r="R100" t="s">
         <v>34</v>
       </c>
-      <c r="R100" s="4">
+      <c r="S100" s="4">
         <v>100</v>
       </c>
-      <c r="S100" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>287</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C101" t="s">
         <v>311</v>
       </c>
-      <c r="C101" s="4">
-        <v>1</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="D101" s="4">
+        <v>1</v>
+      </c>
+      <c r="E101" t="s">
         <v>98</v>
       </c>
-      <c r="E101" s="4">
-        <v>2</v>
-      </c>
       <c r="F101" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" s="4">
         <v>1</v>
       </c>
-      <c r="H101">
-        <v>0</v>
+      <c r="H101" s="4">
+        <v>1</v>
       </c>
       <c r="I101">
         <v>0</v>
       </c>
-      <c r="J101" s="1" t="s">
-        <v>7</v>
+      <c r="J101">
+        <v>0</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M101" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M101" t="s">
-        <v>294</v>
       </c>
       <c r="N101" t="s">
         <v>294</v>
       </c>
       <c r="O101" t="s">
+        <v>294</v>
+      </c>
+      <c r="P101" t="s">
         <v>295</v>
       </c>
-      <c r="P101" t="s">
+      <c r="Q101" t="s">
         <v>300</v>
       </c>
-      <c r="Q101" t="s">
+      <c r="R101" t="s">
         <v>34</v>
       </c>
-      <c r="R101" s="4">
+      <c r="S101" s="4">
         <v>100</v>
       </c>
-      <c r="S101" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>288</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" t="s">
         <v>311</v>
       </c>
-      <c r="C102" s="4">
-        <v>1</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="D102" s="4">
+        <v>1</v>
+      </c>
+      <c r="E102" t="s">
         <v>98</v>
       </c>
-      <c r="E102" s="4">
-        <v>2</v>
-      </c>
       <c r="F102" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G102" s="4">
         <v>1</v>
       </c>
-      <c r="H102">
-        <v>0</v>
+      <c r="H102" s="4">
+        <v>1</v>
       </c>
       <c r="I102">
         <v>0</v>
       </c>
-      <c r="J102" s="1" t="s">
-        <v>7</v>
+      <c r="J102">
+        <v>0</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M102" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M102" t="s">
-        <v>296</v>
       </c>
       <c r="N102" t="s">
         <v>296</v>
       </c>
       <c r="O102" t="s">
+        <v>296</v>
+      </c>
+      <c r="P102" t="s">
         <v>295</v>
       </c>
-      <c r="P102" t="s">
+      <c r="Q102" t="s">
         <v>300</v>
       </c>
-      <c r="Q102" t="s">
+      <c r="R102" t="s">
         <v>34</v>
       </c>
-      <c r="R102" s="4">
+      <c r="S102" s="4">
         <v>100</v>
       </c>
-      <c r="S102" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T102" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>289</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C103" t="s">
         <v>303</v>
       </c>
-      <c r="C103" s="4">
-        <v>1</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="D103" s="4">
+        <v>1</v>
+      </c>
+      <c r="E103" t="s">
         <v>98</v>
       </c>
-      <c r="E103" s="4">
-        <v>2</v>
-      </c>
       <c r="F103" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="4">
         <v>1</v>
       </c>
-      <c r="H103">
-        <v>0</v>
+      <c r="H103" s="4">
+        <v>1</v>
       </c>
       <c r="I103">
         <v>0</v>
       </c>
-      <c r="J103" s="1" t="s">
-        <v>7</v>
+      <c r="J103">
+        <v>0</v>
       </c>
       <c r="K103" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M103" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M103" t="s">
-        <v>297</v>
       </c>
       <c r="N103" t="s">
         <v>297</v>
       </c>
       <c r="O103" t="s">
+        <v>297</v>
+      </c>
+      <c r="P103" t="s">
         <v>298</v>
       </c>
-      <c r="P103" t="s">
+      <c r="Q103" t="s">
         <v>300</v>
       </c>
-      <c r="Q103" t="s">
+      <c r="R103" t="s">
         <v>34</v>
       </c>
-      <c r="R103" s="4">
+      <c r="S103" s="4">
         <v>100</v>
       </c>
-      <c r="S103" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C104" s="5">
-        <v>1</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="5">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E104" s="5">
-        <v>2</v>
-      </c>
       <c r="F104" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="5">
         <v>1</v>
       </c>
-      <c r="H104">
-        <v>0</v>
+      <c r="H104" s="5">
+        <v>1</v>
       </c>
       <c r="I104">
         <v>0</v>
       </c>
-      <c r="J104" s="3" t="s">
-        <v>7</v>
+      <c r="J104">
+        <v>0</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>7</v>
       </c>
       <c r="L104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M104" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="M104" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="N104" s="2" t="s">
         <v>299</v>
       </c>
       <c r="O104" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="P104" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="P104" s="2" t="s">
+      <c r="Q104" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="Q104" s="2" t="s">
+      <c r="R104" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R104" s="5">
+      <c r="S104" s="5">
         <v>100</v>
       </c>
-      <c r="S104" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T104" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C105" s="4">
-        <v>1</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="4">
+        <v>1</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E105" s="16">
+      <c r="F105" s="16">
         <v>3</v>
       </c>
-      <c r="F105" s="4">
-        <v>1</v>
-      </c>
       <c r="G105" s="4">
         <v>1</v>
       </c>
-      <c r="H105">
-        <v>0</v>
+      <c r="H105" s="4">
+        <v>1</v>
       </c>
       <c r="I105">
         <v>0</v>
       </c>
-      <c r="J105" s="1" t="s">
-        <v>334</v>
+      <c r="J105">
+        <v>0</v>
       </c>
       <c r="K105" s="1" t="s">
         <v>334</v>
       </c>
       <c r="L105" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="M105" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M105" t="s">
-        <v>321</v>
       </c>
       <c r="N105" t="s">
         <v>321</v>
       </c>
       <c r="O105" t="s">
+        <v>321</v>
+      </c>
+      <c r="P105" t="s">
         <v>322</v>
       </c>
-      <c r="P105" t="s">
+      <c r="Q105" t="s">
         <v>329</v>
       </c>
-      <c r="Q105" t="s">
+      <c r="R105" t="s">
         <v>34</v>
       </c>
-      <c r="R105" s="4">
+      <c r="S105" s="4">
         <v>61.18</v>
       </c>
-      <c r="S105" s="4">
+      <c r="T105" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C106" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C106" s="4">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="4">
+        <v>1</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E106" s="16">
+      <c r="F106" s="16">
         <v>3</v>
       </c>
-      <c r="F106" s="4">
-        <v>1</v>
-      </c>
       <c r="G106" s="4">
         <v>1</v>
       </c>
-      <c r="H106">
-        <v>0</v>
+      <c r="H106" s="4">
+        <v>1</v>
       </c>
       <c r="I106">
         <v>0</v>
       </c>
-      <c r="J106" s="1" t="s">
-        <v>334</v>
+      <c r="J106">
+        <v>0</v>
       </c>
       <c r="K106" s="1" t="s">
         <v>334</v>
       </c>
       <c r="L106" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="M106" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="M106" t="s">
-        <v>323</v>
       </c>
       <c r="N106" t="s">
         <v>323</v>
       </c>
       <c r="O106" t="s">
+        <v>323</v>
+      </c>
+      <c r="P106" t="s">
         <v>322</v>
       </c>
-      <c r="P106" t="s">
+      <c r="Q106" t="s">
         <v>329</v>
       </c>
-      <c r="Q106" t="s">
+      <c r="R106" t="s">
         <v>34</v>
       </c>
-      <c r="R106" s="4">
+      <c r="S106" s="4">
         <v>61.18</v>
       </c>
-      <c r="S106" s="4">
+      <c r="T106" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C107" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C107" s="4">
-        <v>1</v>
-      </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="4">
+        <v>1</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E107" s="16">
+      <c r="F107" s="16">
         <v>3</v>
       </c>
-      <c r="F107" s="4">
-        <v>1</v>
-      </c>
       <c r="G107" s="4">
         <v>1</v>
       </c>
-      <c r="H107">
-        <v>0</v>
+      <c r="H107" s="4">
+        <v>1</v>
       </c>
       <c r="I107">
         <v>0</v>
       </c>
-      <c r="J107" s="1" t="s">
-        <v>423</v>
+      <c r="J107">
+        <v>0</v>
       </c>
       <c r="K107" s="1" t="s">
         <v>423</v>
       </c>
       <c r="L107" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M107" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="M107" t="s">
-        <v>324</v>
       </c>
       <c r="N107" t="s">
         <v>324</v>
       </c>
       <c r="O107" t="s">
+        <v>324</v>
+      </c>
+      <c r="P107" t="s">
         <v>325</v>
       </c>
-      <c r="P107" t="s">
+      <c r="Q107" t="s">
         <v>330</v>
       </c>
-      <c r="Q107" t="s">
+      <c r="R107" t="s">
         <v>34</v>
       </c>
-      <c r="R107" s="4">
+      <c r="S107" s="4">
         <v>61.18</v>
       </c>
-      <c r="S107" s="4">
+      <c r="T107" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C108" s="4">
-        <v>1</v>
-      </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="4">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E108" s="16">
+      <c r="F108" s="16">
         <v>3</v>
       </c>
-      <c r="F108" s="4">
-        <v>1</v>
-      </c>
       <c r="G108" s="4">
         <v>1</v>
       </c>
-      <c r="H108">
-        <v>0</v>
+      <c r="H108" s="4">
+        <v>1</v>
       </c>
       <c r="I108">
         <v>0</v>
       </c>
-      <c r="J108" s="1" t="s">
-        <v>423</v>
+      <c r="J108">
+        <v>1</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L108" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M108" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="M108" t="s">
-        <v>326</v>
       </c>
       <c r="N108" t="s">
         <v>326</v>
       </c>
       <c r="O108" t="s">
+        <v>326</v>
+      </c>
+      <c r="P108" t="s">
         <v>325</v>
       </c>
-      <c r="P108" t="s">
+      <c r="Q108" t="s">
         <v>330</v>
       </c>
-      <c r="Q108" t="s">
+      <c r="R108" t="s">
         <v>34</v>
       </c>
-      <c r="R108" s="4">
+      <c r="S108" s="4">
         <v>61.18</v>
       </c>
-      <c r="S108" s="4">
+      <c r="T108" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C109" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C109" s="4">
-        <v>1</v>
-      </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="4">
+        <v>1</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E109" s="16">
+      <c r="F109" s="16">
         <v>3</v>
       </c>
-      <c r="F109" s="4">
-        <v>1</v>
-      </c>
       <c r="G109" s="4">
         <v>1</v>
       </c>
-      <c r="H109">
-        <v>0</v>
+      <c r="H109" s="4">
+        <v>1</v>
       </c>
       <c r="I109">
         <v>0</v>
       </c>
-      <c r="J109" s="1" t="s">
-        <v>424</v>
+      <c r="J109">
+        <v>0</v>
       </c>
       <c r="K109" s="1" t="s">
         <v>424</v>
       </c>
       <c r="L109" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M109" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="M109" t="s">
-        <v>327</v>
       </c>
       <c r="N109" t="s">
         <v>327</v>
       </c>
       <c r="O109" t="s">
+        <v>327</v>
+      </c>
+      <c r="P109" t="s">
         <v>328</v>
       </c>
-      <c r="P109" t="s">
+      <c r="Q109" t="s">
         <v>331</v>
       </c>
-      <c r="Q109" t="s">
+      <c r="R109" t="s">
         <v>34</v>
       </c>
-      <c r="R109" s="4">
+      <c r="S109" s="4">
         <v>61.18</v>
       </c>
-      <c r="S109" s="4">
+      <c r="T109" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C110" s="4">
-        <v>1</v>
-      </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="4">
+        <v>1</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E110" s="16">
+      <c r="F110" s="16">
         <v>3</v>
       </c>
-      <c r="F110" s="4">
-        <v>1</v>
-      </c>
       <c r="G110" s="4">
         <v>1</v>
       </c>
-      <c r="H110">
-        <v>0</v>
+      <c r="H110" s="4">
+        <v>1</v>
       </c>
       <c r="I110">
-        <v>1</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>424</v>
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
       </c>
       <c r="K110" s="1" t="s">
         <v>424</v>
       </c>
       <c r="L110" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M110" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="M110" t="s">
-        <v>332</v>
       </c>
       <c r="N110" t="s">
         <v>332</v>
       </c>
       <c r="O110" t="s">
+        <v>332</v>
+      </c>
+      <c r="P110" t="s">
         <v>328</v>
       </c>
-      <c r="P110" t="s">
+      <c r="Q110" t="s">
         <v>333</v>
       </c>
-      <c r="Q110" t="s">
+      <c r="R110" t="s">
         <v>34</v>
       </c>
-      <c r="R110" s="4">
+      <c r="S110" s="4">
         <v>61.18</v>
       </c>
-      <c r="S110" s="4">
+      <c r="T110" s="4">
         <v>135</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1 C11 C47:C54 C79:C87 C91:C96 C99:C1048576 C58:C68">
+  <conditionalFormatting sqref="D1 D11 D47:D54 D79:D87 D91:D96 D99:D1048576 D58:D68">
     <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="cellIs" dxfId="33" priority="35" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
+  <conditionalFormatting sqref="D3">
     <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
+  <conditionalFormatting sqref="D4">
     <cfRule type="cellIs" dxfId="31" priority="33" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
+  <conditionalFormatting sqref="D5">
     <cfRule type="cellIs" dxfId="30" priority="32" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
+  <conditionalFormatting sqref="D6">
     <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
+  <conditionalFormatting sqref="D7">
     <cfRule type="cellIs" dxfId="28" priority="30" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
+  <conditionalFormatting sqref="D8">
     <cfRule type="cellIs" dxfId="27" priority="29" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
+  <conditionalFormatting sqref="D9">
     <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="D10">
     <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="D12">
     <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
+  <conditionalFormatting sqref="D13">
     <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
+  <conditionalFormatting sqref="D14">
     <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
+  <conditionalFormatting sqref="D15">
     <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
+  <conditionalFormatting sqref="D16">
     <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17">
+  <conditionalFormatting sqref="D17">
     <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
+  <conditionalFormatting sqref="D18">
     <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:C20">
+  <conditionalFormatting sqref="D19:D20">
     <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21">
+  <conditionalFormatting sqref="D21">
     <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
+  <conditionalFormatting sqref="D22">
     <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
+  <conditionalFormatting sqref="D23">
     <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24">
+  <conditionalFormatting sqref="D24">
     <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25">
+  <conditionalFormatting sqref="D25">
     <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26">
+  <conditionalFormatting sqref="D26">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27">
+  <conditionalFormatting sqref="D27">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
+  <conditionalFormatting sqref="D28">
     <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C46">
+  <conditionalFormatting sqref="D29:D46">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70:C78">
+  <conditionalFormatting sqref="D70:D78">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C69">
+  <conditionalFormatting sqref="D69">
     <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C97">
+  <conditionalFormatting sqref="D97">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C98">
+  <conditionalFormatting sqref="D98">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C88:C90">
+  <conditionalFormatting sqref="D88:D90">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C57">
+  <conditionalFormatting sqref="D57">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C56">
+  <conditionalFormatting sqref="D56">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C55">
+  <conditionalFormatting sqref="D55">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
